--- a/agriculture 48.xlsx
+++ b/agriculture 48.xlsx
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
-  <si>
-    <t xml:space="preserve">Annual Growth rate APY Statistics of Cashew in India(1962-2020)</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t xml:space="preserve">Year</t>
   </si>
@@ -153,7 +150,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -175,14 +172,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -249,16 +238,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -278,7 +263,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -303,454 +288,453 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H38"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:H1048576"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
+      <c r="B3" s="3" t="n">
+        <v>0.375939849624052</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>3.38983050847457</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>3.00265098916159</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="4" t="n">
-        <v>0.375939849624052</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>3.38983050847457</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>3.00265098916159</v>
+      <c r="B4" s="3" t="n">
+        <v>4.86891385767789</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>14.4262295081967</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>9.11303312556904</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="4" t="n">
-        <v>4.86891385767789</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>14.4262295081967</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>9.11303312556904</v>
+      <c r="B5" s="3" t="n">
+        <v>0.89285714285714</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>-0.286532951289398</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>-1.16814556890937</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="4" t="n">
-        <v>0.89285714285714</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>-0.286532951289398</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>-1.16814556890937</v>
+      <c r="B6" s="3" t="n">
+        <v>2.12389380530973</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>-7.47126436781609</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>-9.39554819541182</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="4" t="n">
-        <v>2.12389380530973</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>-7.47126436781609</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>-9.39554819541182</v>
+      <c r="B7" s="3" t="n">
+        <v>10.051993067591</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>29.8136645962733</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>17.9568505178655</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="4" t="n">
-        <v>10.051993067591</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>29.8136645962733</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>17.9568505178655</v>
+      <c r="B8" s="3" t="n">
+        <v>3.77952755905513</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>2.87081339712918</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>-0.876540021571692</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="4" t="n">
-        <v>3.77952755905513</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>2.87081339712918</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>-0.876540021571692</v>
+      <c r="B9" s="3" t="n">
+        <v>2.42792109256449</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>-16.2790697674419</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>-18.263601532567</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="4" t="n">
-        <v>2.42792109256449</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>-16.2790697674419</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>-18.263601532567</v>
+      <c r="B10" s="3" t="n">
+        <v>4.59259259259259</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>27.7777777777778</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>22.1682635516472</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="4" t="n">
-        <v>4.59259259259259</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>27.7777777777778</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>22.1682635516472</v>
+      <c r="B11" s="3" t="n">
+        <v>-2.83286118980169</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>13.0434782608696</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>16.3392473448339</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="4" t="n">
-        <v>-2.83286118980169</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>13.0434782608696</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>16.3392473448339</v>
+      <c r="B12" s="3" t="n">
+        <v>4.95626822157433</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>-13.4615384615385</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>-17.5483496477666</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="4" t="n">
-        <v>4.95626822157433</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>-13.4615384615385</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>-17.5483496477666</v>
+      <c r="B13" s="3" t="n">
+        <v>2.77777777777777</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>2.22222222222221</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>-0.540799999999997</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="4" t="n">
-        <v>2.77777777777777</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>2.22222222222221</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>-0.540799999999997</v>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>0</v>
+      <c r="B15" s="3" t="n">
+        <v>5.40540540540539</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>16.304347826087</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>10.3407226279721</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="4" t="n">
-        <v>5.40540540540539</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>16.304347826087</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>10.3407226279721</v>
+      <c r="B16" s="3" t="n">
+        <v>5.12820512820513</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>1.6822429906542</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>-3.2789036302668</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="4" t="n">
-        <v>5.12820512820513</v>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>1.6822429906542</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>-3.2789036302668</v>
+      <c r="B17" s="3" t="n">
+        <v>2.80487804878049</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>6.43382352941178</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>3.53024524803667</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="4" t="n">
-        <v>2.80487804878049</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>6.43382352941178</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>3.53024524803667</v>
+      <c r="B18" s="3" t="n">
+        <v>1.30486358244366</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>7.08117443868739</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>5.70301239025668</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="4" t="n">
-        <v>1.30486358244366</v>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>7.08117443868739</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>5.70301239025668</v>
+      <c r="B19" s="3" t="n">
+        <v>1.63934426229508</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>7.25806451612903</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>5.52754820936638</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="4" t="n">
-        <v>1.63934426229508</v>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>7.25806451612903</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>5.52754820936638</v>
+      <c r="B20" s="3" t="n">
+        <v>2.88018433179724</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>4.51127819548873</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>1.58589273360918</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="4" t="n">
-        <v>2.88018433179724</v>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>4.51127819548873</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>1.58589273360918</v>
+      <c r="B21" s="3" t="n">
+        <v>3.35946248600223</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>-11.7985611510791</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>-14.6656730225626</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="4" t="n">
-        <v>3.35946248600223</v>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>-11.7985611510791</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>-14.6656730225626</v>
+      <c r="B22" s="3" t="n">
+        <v>3.27193932827736</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>10.0489396411093</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>6.56186948534949</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="4" t="n">
-        <v>3.27193932827736</v>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>10.0489396411093</v>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>6.56186948534949</v>
+      <c r="B23" s="3" t="n">
+        <v>2.69618128409568</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>7.51556477912836</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>4.69253377041767</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="4" t="n">
-        <v>2.69618128409568</v>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>7.51556477912836</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>4.69253377041767</v>
+      <c r="B24" s="3" t="n">
+        <v>1.29737460414752</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>3.87425892734041</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>2.54409998245448</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B25" s="4" t="n">
-        <v>1.29737460414752</v>
-      </c>
-      <c r="C25" s="4" t="n">
-        <v>3.87425892734041</v>
-      </c>
-      <c r="D25" s="4" t="n">
-        <v>2.54409998245448</v>
+      <c r="B25" s="3" t="n">
+        <v>1.94130697862041</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>-0.0318555880010618</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>-1.934770591487</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B26" s="4" t="n">
-        <v>1.94130697862041</v>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>-0.0318555880010618</v>
-      </c>
-      <c r="D26" s="4" t="n">
-        <v>-1.934770591487</v>
+      <c r="B26" s="3" t="n">
+        <v>1.80442202107136</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>-1.51229486430506</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>-3.25736833628605</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B27" s="4" t="n">
-        <v>1.80442202107136</v>
-      </c>
-      <c r="C27" s="4" t="n">
-        <v>-1.51229486430506</v>
-      </c>
-      <c r="D27" s="4" t="n">
-        <v>-3.25736833628605</v>
+      <c r="B27" s="3" t="n">
+        <v>0.671467024264172</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>-9.54069320678916</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>-10.1455307223818</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B28" s="4" t="n">
-        <v>0.671467024264172</v>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>-9.54069320678916</v>
-      </c>
-      <c r="D28" s="4" t="n">
-        <v>-10.1455307223818</v>
+      <c r="B28" s="3" t="n">
+        <v>-5.5984555984556</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>11.0283159463487</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>17.6136363636364</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B29" s="4" t="n">
-        <v>-5.5984555984556</v>
-      </c>
-      <c r="C29" s="4" t="n">
-        <v>11.0283159463487</v>
-      </c>
-      <c r="D29" s="4" t="n">
-        <v>17.6136363636364</v>
+      <c r="B29" s="3" t="n">
+        <v>8.58895705521472</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>9.66442953020135</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>0.989813064482248</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B30" s="4" t="n">
-        <v>8.58895705521472</v>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>9.66442953020135</v>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>0.989813064482248</v>
+      <c r="B30" s="3" t="n">
+        <v>4.08380414312617</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>-9.09302325581395</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>-12.6595606395424</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B31" s="4" t="n">
-        <v>4.08380414312617</v>
-      </c>
-      <c r="C31" s="4" t="n">
-        <v>-9.09302325581395</v>
-      </c>
-      <c r="D31" s="4" t="n">
-        <v>-12.6595606395424</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="3" t="s">
+      <c r="B31" s="3" t="n">
+        <v>1.68540850574921</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>-6.96234061746847</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>-3.60613772677889</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B32" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B32" s="4" t="n">
-        <v>1.68540850574921</v>
-      </c>
-      <c r="C32" s="4" t="n">
-        <v>-6.96234061746847</v>
-      </c>
-      <c r="D32" s="4" t="n">
-        <v>-3.60613772677889</v>
-      </c>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
     </row>
     <row r="33" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C33" s="5"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
       <c r="F33" s="6"/>
       <c r="G33" s="6"/>
       <c r="H33" s="6"/>
@@ -767,58 +751,47 @@
       <c r="H34" s="7"/>
     </row>
     <row r="35" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="8" t="s">
+      <c r="B35" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C35" s="8"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8"/>
-      <c r="G35" s="8"/>
-      <c r="H35" s="8"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="7"/>
+      <c r="H35" s="7"/>
     </row>
     <row r="36" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="8" t="s">
+      <c r="B36" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="8"/>
-      <c r="H36" s="8"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="7"/>
+      <c r="H36" s="7"/>
     </row>
     <row r="37" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="8" t="s">
+      <c r="B37" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
-      <c r="G37" s="8"/>
-      <c r="H37" s="8"/>
-    </row>
-    <row r="38" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C38" s="8"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
-      <c r="G38" s="8"/>
-      <c r="H38" s="8"/>
-    </row>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="7"/>
+      <c r="H37" s="7"/>
+    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B33:E33"/>
+  <mergeCells count="6">
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B33:H33"/>
     <mergeCell ref="B34:H34"/>
     <mergeCell ref="B35:H35"/>
     <mergeCell ref="B36:H36"/>
     <mergeCell ref="B37:H37"/>
-    <mergeCell ref="B38:H38"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>

--- a/agriculture 48.xlsx
+++ b/agriculture 48.xlsx
@@ -25,13 +25,13 @@
     <t xml:space="preserve">Year</t>
   </si>
   <si>
-    <t xml:space="preserve">Area(kha)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production (k/t)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yield (Kg./ha)</t>
+    <t xml:space="preserve">Area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yield </t>
   </si>
   <si>
     <t xml:space="preserve">1990-91</t>
@@ -124,13 +124,31 @@
     <t xml:space="preserve">2019-20</t>
   </si>
   <si>
+    <t xml:space="preserve">Unit:- </t>
+  </si>
+  <si>
     <t xml:space="preserve">Source: EPWRF (Economic and Political Weekly Research Foundation )1962-2020</t>
   </si>
   <si>
-    <t xml:space="preserve">Source Description:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1962-63 to 1969-70: Plantation Crops: Cashewnut:-&gt; Directorate of Economics and Statistics, Dept. of Agriculture, Cooperation and Farmers Welfare, Ministry of Agriculture, Govt. of India</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Source Description: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">1962-63 to 1969-70: Plantation Crops: Cashewnut:-&gt; Directorate of Economics and Statistics, Dept. of Agriculture, Cooperation and Farmers Welfare, Ministry of Agriculture, Govt. of India</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">1993-94 to 2007-08: Plantation Crops: Cashewnut:-&gt; Directorate of Cashewnut and Cocoa Development, Ministry of Agriculture and Farmers Welfare, Govt. of India</t>
@@ -150,7 +168,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -179,7 +197,20 @@
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -238,32 +269,48 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -291,507 +338,509 @@
   <dimension ref="A1:H1048576"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1"/>
+      <c r="E1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B3" s="5" t="n">
         <v>0.375939849624052</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" s="5" t="n">
         <v>3.38983050847457</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="5" t="n">
         <v>3.00265098916159</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="5" t="n">
         <v>4.86891385767789</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C4" s="5" t="n">
         <v>14.4262295081967</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="5" t="n">
         <v>9.11303312556904</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" s="5" t="n">
         <v>0.89285714285714</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C5" s="5" t="n">
         <v>-0.286532951289398</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="5" t="n">
         <v>-1.16814556890937</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" s="5" t="n">
         <v>2.12389380530973</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C6" s="5" t="n">
         <v>-7.47126436781609</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="5" t="n">
         <v>-9.39554819541182</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B7" s="5" t="n">
         <v>10.051993067591</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C7" s="5" t="n">
         <v>29.8136645962733</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="5" t="n">
         <v>17.9568505178655</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" s="5" t="n">
         <v>3.77952755905513</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="C8" s="5" t="n">
         <v>2.87081339712918</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="5" t="n">
         <v>-0.876540021571692</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="3" t="n">
+      <c r="B9" s="5" t="n">
         <v>2.42792109256449</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="C9" s="5" t="n">
         <v>-16.2790697674419</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" s="5" t="n">
         <v>-18.263601532567</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B10" s="5" t="n">
         <v>4.59259259259259</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="C10" s="5" t="n">
         <v>27.7777777777778</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D10" s="5" t="n">
         <v>22.1682635516472</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" s="5" t="n">
         <v>-2.83286118980169</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="C11" s="5" t="n">
         <v>13.0434782608696</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="D11" s="5" t="n">
         <v>16.3392473448339</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B12" s="5" t="n">
         <v>4.95626822157433</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="C12" s="5" t="n">
         <v>-13.4615384615385</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" s="5" t="n">
         <v>-17.5483496477666</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="3" t="n">
+      <c r="B13" s="5" t="n">
         <v>2.77777777777777</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="C13" s="5" t="n">
         <v>2.22222222222221</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="D13" s="5" t="n">
         <v>-0.540799999999997</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B14" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C14" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D14" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="3" t="n">
+      <c r="B15" s="5" t="n">
         <v>5.40540540540539</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="C15" s="5" t="n">
         <v>16.304347826087</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="D15" s="5" t="n">
         <v>10.3407226279721</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="3" t="n">
+      <c r="B16" s="5" t="n">
         <v>5.12820512820513</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="C16" s="5" t="n">
         <v>1.6822429906542</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D16" s="5" t="n">
         <v>-3.2789036302668</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="3" t="n">
+      <c r="B17" s="5" t="n">
         <v>2.80487804878049</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="C17" s="5" t="n">
         <v>6.43382352941178</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="D17" s="5" t="n">
         <v>3.53024524803667</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="3" t="n">
+      <c r="B18" s="5" t="n">
         <v>1.30486358244366</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="C18" s="5" t="n">
         <v>7.08117443868739</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="D18" s="5" t="n">
         <v>5.70301239025668</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="3" t="n">
+      <c r="B19" s="5" t="n">
         <v>1.63934426229508</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="C19" s="5" t="n">
         <v>7.25806451612903</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="D19" s="5" t="n">
         <v>5.52754820936638</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="3" t="n">
+      <c r="B20" s="5" t="n">
         <v>2.88018433179724</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="C20" s="5" t="n">
         <v>4.51127819548873</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="D20" s="5" t="n">
         <v>1.58589273360918</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="3" t="n">
+      <c r="B21" s="5" t="n">
         <v>3.35946248600223</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="C21" s="5" t="n">
         <v>-11.7985611510791</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="D21" s="5" t="n">
         <v>-14.6656730225626</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="3" t="n">
+      <c r="B22" s="5" t="n">
         <v>3.27193932827736</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="C22" s="5" t="n">
         <v>10.0489396411093</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="D22" s="5" t="n">
         <v>6.56186948534949</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="3" t="n">
+      <c r="B23" s="5" t="n">
         <v>2.69618128409568</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="C23" s="5" t="n">
         <v>7.51556477912836</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="D23" s="5" t="n">
         <v>4.69253377041767</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="3" t="n">
+      <c r="B24" s="5" t="n">
         <v>1.29737460414752</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="C24" s="5" t="n">
         <v>3.87425892734041</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="D24" s="5" t="n">
         <v>2.54409998245448</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B25" s="3" t="n">
+      <c r="B25" s="5" t="n">
         <v>1.94130697862041</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="C25" s="5" t="n">
         <v>-0.0318555880010618</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="D25" s="5" t="n">
         <v>-1.934770591487</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B26" s="3" t="n">
+      <c r="B26" s="5" t="n">
         <v>1.80442202107136</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="C26" s="5" t="n">
         <v>-1.51229486430506</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="D26" s="5" t="n">
         <v>-3.25736833628605</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B27" s="3" t="n">
+      <c r="B27" s="5" t="n">
         <v>0.671467024264172</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="C27" s="5" t="n">
         <v>-9.54069320678916</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="D27" s="5" t="n">
         <v>-10.1455307223818</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B28" s="3" t="n">
+      <c r="B28" s="5" t="n">
         <v>-5.5984555984556</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="C28" s="5" t="n">
         <v>11.0283159463487</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="D28" s="5" t="n">
         <v>17.6136363636364</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B29" s="3" t="n">
+      <c r="B29" s="5" t="n">
         <v>8.58895705521472</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="C29" s="5" t="n">
         <v>9.66442953020135</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="D29" s="5" t="n">
         <v>0.989813064482248</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B30" s="3" t="n">
+      <c r="B30" s="5" t="n">
         <v>4.08380414312617</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="C30" s="5" t="n">
         <v>-9.09302325581395</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="D30" s="5" t="n">
         <v>-12.6595606395424</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B31" s="3" t="n">
+      <c r="B31" s="5" t="n">
         <v>1.68540850574921</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="C31" s="5" t="n">
         <v>-6.96234061746847</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="D31" s="5" t="n">
         <v>-3.60613772677889</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="4" t="s">
+    <row r="32" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="4" t="s">
         <v>34</v>
       </c>
+      <c r="B32" s="4"/>
       <c r="C32" s="4"/>
       <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="5"/>
-      <c r="G32" s="5"/>
-      <c r="H32" s="5"/>
     </row>
     <row r="33" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="6" t="s">
+      <c r="A33" s="6" t="s">
         <v>35</v>
       </c>
+      <c r="B33" s="6"/>
       <c r="C33" s="6"/>
       <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="6"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
     </row>
     <row r="34" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="7" t="s">
+      <c r="A34" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
-      <c r="G34" s="7"/>
-      <c r="H34" s="7"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="10"/>
+      <c r="G34" s="10"/>
+      <c r="H34" s="10"/>
     </row>
     <row r="35" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="7" t="s">
+      <c r="A35" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
-      <c r="G35" s="7"/>
-      <c r="H35" s="7"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11"/>
     </row>
     <row r="36" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="7" t="s">
+      <c r="A36" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="7"/>
-      <c r="G36" s="7"/>
-      <c r="H36" s="7"/>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11"/>
     </row>
     <row r="37" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="7" t="s">
+      <c r="A37" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
-      <c r="G37" s="7"/>
-      <c r="H37" s="7"/>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
     </row>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="B32:E32"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B34:H34"/>
-    <mergeCell ref="B35:H35"/>
-    <mergeCell ref="B36:H36"/>
-    <mergeCell ref="B37:H37"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A37:D37"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>

--- a/agriculture 48.xlsx
+++ b/agriculture 48.xlsx
@@ -124,7 +124,7 @@
     <t xml:space="preserve">2019-20</t>
   </si>
   <si>
-    <t xml:space="preserve">Unit:- </t>
+    <t xml:space="preserve">Unit:- Percentage(%)</t>
   </si>
   <si>
     <t xml:space="preserve">Source: EPWRF (Economic and Political Weekly Research Foundation )1962-2020</t>
@@ -137,6 +137,7 @@
         <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Source Description: </t>
     </r>
@@ -146,6 +147,7 @@
         <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">1962-63 to 1969-70: Plantation Crops: Cashewnut:-&gt; Directorate of Economics and Statistics, Dept. of Agriculture, Cooperation and Farmers Welfare, Ministry of Agriculture, Govt. of India</t>
     </r>
@@ -168,7 +170,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -197,20 +199,7 @@
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -269,7 +258,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -278,11 +267,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -294,7 +279,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -306,11 +291,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -342,495 +327,495 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3"/>
+      <c r="E1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="4" t="n">
         <v>0.375939849624052</v>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3" s="4" t="n">
         <v>3.38983050847457</v>
       </c>
-      <c r="D3" s="5" t="n">
+      <c r="D3" s="4" t="n">
         <v>3.00265098916159</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="4" t="n">
         <v>4.86891385767789</v>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="4" t="n">
         <v>14.4262295081967</v>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="D4" s="4" t="n">
         <v>9.11303312556904</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="4" t="n">
         <v>0.89285714285714</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="4" t="n">
         <v>-0.286532951289398</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="4" t="n">
         <v>-1.16814556890937</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="4" t="n">
         <v>2.12389380530973</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="4" t="n">
         <v>-7.47126436781609</v>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="D6" s="4" t="n">
         <v>-9.39554819541182</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="4" t="n">
         <v>10.051993067591</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="4" t="n">
         <v>29.8136645962733</v>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D7" s="4" t="n">
         <v>17.9568505178655</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="4" t="n">
         <v>3.77952755905513</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="4" t="n">
         <v>2.87081339712918</v>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D8" s="4" t="n">
         <v>-0.876540021571692</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="4" t="n">
         <v>2.42792109256449</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="4" t="n">
         <v>-16.2790697674419</v>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D9" s="4" t="n">
         <v>-18.263601532567</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="4" t="n">
         <v>4.59259259259259</v>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C10" s="4" t="n">
         <v>27.7777777777778</v>
       </c>
-      <c r="D10" s="5" t="n">
+      <c r="D10" s="4" t="n">
         <v>22.1682635516472</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="4" t="n">
         <v>-2.83286118980169</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="4" t="n">
         <v>13.0434782608696</v>
       </c>
-      <c r="D11" s="5" t="n">
+      <c r="D11" s="4" t="n">
         <v>16.3392473448339</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="4" t="n">
         <v>4.95626822157433</v>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C12" s="4" t="n">
         <v>-13.4615384615385</v>
       </c>
-      <c r="D12" s="5" t="n">
+      <c r="D12" s="4" t="n">
         <v>-17.5483496477666</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="4" t="n">
         <v>2.77777777777777</v>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C13" s="4" t="n">
         <v>2.22222222222221</v>
       </c>
-      <c r="D13" s="5" t="n">
+      <c r="D13" s="4" t="n">
         <v>-0.540799999999997</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B14" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="C14" s="5" t="n">
+      <c r="C14" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="5" t="n">
+      <c r="D14" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="4" t="n">
         <v>5.40540540540539</v>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C15" s="4" t="n">
         <v>16.304347826087</v>
       </c>
-      <c r="D15" s="5" t="n">
+      <c r="D15" s="4" t="n">
         <v>10.3407226279721</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B16" s="4" t="n">
         <v>5.12820512820513</v>
       </c>
-      <c r="C16" s="5" t="n">
+      <c r="C16" s="4" t="n">
         <v>1.6822429906542</v>
       </c>
-      <c r="D16" s="5" t="n">
+      <c r="D16" s="4" t="n">
         <v>-3.2789036302668</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="5" t="n">
+      <c r="B17" s="4" t="n">
         <v>2.80487804878049</v>
       </c>
-      <c r="C17" s="5" t="n">
+      <c r="C17" s="4" t="n">
         <v>6.43382352941178</v>
       </c>
-      <c r="D17" s="5" t="n">
+      <c r="D17" s="4" t="n">
         <v>3.53024524803667</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="5" t="n">
+      <c r="B18" s="4" t="n">
         <v>1.30486358244366</v>
       </c>
-      <c r="C18" s="5" t="n">
+      <c r="C18" s="4" t="n">
         <v>7.08117443868739</v>
       </c>
-      <c r="D18" s="5" t="n">
+      <c r="D18" s="4" t="n">
         <v>5.70301239025668</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="5" t="n">
+      <c r="B19" s="4" t="n">
         <v>1.63934426229508</v>
       </c>
-      <c r="C19" s="5" t="n">
+      <c r="C19" s="4" t="n">
         <v>7.25806451612903</v>
       </c>
-      <c r="D19" s="5" t="n">
+      <c r="D19" s="4" t="n">
         <v>5.52754820936638</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="5" t="n">
+      <c r="B20" s="4" t="n">
         <v>2.88018433179724</v>
       </c>
-      <c r="C20" s="5" t="n">
+      <c r="C20" s="4" t="n">
         <v>4.51127819548873</v>
       </c>
-      <c r="D20" s="5" t="n">
+      <c r="D20" s="4" t="n">
         <v>1.58589273360918</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="5" t="n">
+      <c r="B21" s="4" t="n">
         <v>3.35946248600223</v>
       </c>
-      <c r="C21" s="5" t="n">
+      <c r="C21" s="4" t="n">
         <v>-11.7985611510791</v>
       </c>
-      <c r="D21" s="5" t="n">
+      <c r="D21" s="4" t="n">
         <v>-14.6656730225626</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="5" t="n">
+      <c r="B22" s="4" t="n">
         <v>3.27193932827736</v>
       </c>
-      <c r="C22" s="5" t="n">
+      <c r="C22" s="4" t="n">
         <v>10.0489396411093</v>
       </c>
-      <c r="D22" s="5" t="n">
+      <c r="D22" s="4" t="n">
         <v>6.56186948534949</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="5" t="n">
+      <c r="B23" s="4" t="n">
         <v>2.69618128409568</v>
       </c>
-      <c r="C23" s="5" t="n">
+      <c r="C23" s="4" t="n">
         <v>7.51556477912836</v>
       </c>
-      <c r="D23" s="5" t="n">
+      <c r="D23" s="4" t="n">
         <v>4.69253377041767</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="5" t="n">
+      <c r="B24" s="4" t="n">
         <v>1.29737460414752</v>
       </c>
-      <c r="C24" s="5" t="n">
+      <c r="C24" s="4" t="n">
         <v>3.87425892734041</v>
       </c>
-      <c r="D24" s="5" t="n">
+      <c r="D24" s="4" t="n">
         <v>2.54409998245448</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B25" s="5" t="n">
+      <c r="B25" s="4" t="n">
         <v>1.94130697862041</v>
       </c>
-      <c r="C25" s="5" t="n">
+      <c r="C25" s="4" t="n">
         <v>-0.0318555880010618</v>
       </c>
-      <c r="D25" s="5" t="n">
+      <c r="D25" s="4" t="n">
         <v>-1.934770591487</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B26" s="5" t="n">
+      <c r="B26" s="4" t="n">
         <v>1.80442202107136</v>
       </c>
-      <c r="C26" s="5" t="n">
+      <c r="C26" s="4" t="n">
         <v>-1.51229486430506</v>
       </c>
-      <c r="D26" s="5" t="n">
+      <c r="D26" s="4" t="n">
         <v>-3.25736833628605</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B27" s="5" t="n">
+      <c r="B27" s="4" t="n">
         <v>0.671467024264172</v>
       </c>
-      <c r="C27" s="5" t="n">
+      <c r="C27" s="4" t="n">
         <v>-9.54069320678916</v>
       </c>
-      <c r="D27" s="5" t="n">
+      <c r="D27" s="4" t="n">
         <v>-10.1455307223818</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B28" s="5" t="n">
+      <c r="B28" s="4" t="n">
         <v>-5.5984555984556</v>
       </c>
-      <c r="C28" s="5" t="n">
+      <c r="C28" s="4" t="n">
         <v>11.0283159463487</v>
       </c>
-      <c r="D28" s="5" t="n">
+      <c r="D28" s="4" t="n">
         <v>17.6136363636364</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B29" s="5" t="n">
+      <c r="B29" s="4" t="n">
         <v>8.58895705521472</v>
       </c>
-      <c r="C29" s="5" t="n">
+      <c r="C29" s="4" t="n">
         <v>9.66442953020135</v>
       </c>
-      <c r="D29" s="5" t="n">
+      <c r="D29" s="4" t="n">
         <v>0.989813064482248</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B30" s="5" t="n">
+      <c r="B30" s="4" t="n">
         <v>4.08380414312617</v>
       </c>
-      <c r="C30" s="5" t="n">
+      <c r="C30" s="4" t="n">
         <v>-9.09302325581395</v>
       </c>
-      <c r="D30" s="5" t="n">
+      <c r="D30" s="4" t="n">
         <v>-12.6595606395424</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B31" s="5" t="n">
+      <c r="B31" s="4" t="n">
         <v>1.68540850574921</v>
       </c>
-      <c r="C31" s="5" t="n">
+      <c r="C31" s="4" t="n">
         <v>-6.96234061746847</v>
       </c>
-      <c r="D31" s="5" t="n">
+      <c r="D31" s="4" t="n">
         <v>-3.60613772677889</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
     </row>
     <row r="33" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="s">
+      <c r="A33" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="8"/>
-      <c r="H33" s="8"/>
+      <c r="B33" s="5"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="7"/>
+      <c r="H33" s="7"/>
     </row>
     <row r="34" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="9" t="s">
+      <c r="A34" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="10"/>
-      <c r="F34" s="10"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="10"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="9"/>
     </row>
     <row r="35" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="6" t="s">
+      <c r="A35" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="11"/>
+      <c r="B35" s="5"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="10"/>
+      <c r="F35" s="10"/>
+      <c r="G35" s="10"/>
+      <c r="H35" s="10"/>
     </row>
     <row r="36" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="6" t="s">
+      <c r="A36" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="6"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="11"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="11"/>
-      <c r="H36" s="11"/>
+      <c r="B36" s="5"/>
+      <c r="C36" s="5"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="10"/>
+      <c r="F36" s="10"/>
+      <c r="G36" s="10"/>
+      <c r="H36" s="10"/>
     </row>
     <row r="37" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="6" t="s">
+      <c r="A37" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="6"/>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="11"/>
-      <c r="F37" s="11"/>
-      <c r="G37" s="11"/>
-      <c r="H37" s="11"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="5"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="10"/>
+      <c r="G37" s="10"/>
+      <c r="H37" s="10"/>
     </row>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>

--- a/agriculture 48.xlsx
+++ b/agriculture 48.xlsx
@@ -124,7 +124,7 @@
     <t xml:space="preserve">2019-20</t>
   </si>
   <si>
-    <t xml:space="preserve">Unit:- Percentage(%)</t>
+    <t xml:space="preserve">Unit:- Percentage (%)</t>
   </si>
   <si>
     <t xml:space="preserve">Source: EPWRF (Economic and Political Weekly Research Foundation )1962-2020</t>
